--- a/data/export/2026-10-30-operations.xlsx
+++ b/data/export/2026-10-30-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,17 +828,17 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -836,13 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -908,7 +924,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -947,7 +963,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -958,7 +974,7 @@
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1040,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1079,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1090,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1123,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1140,7 +1160,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,17 +1184,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1184,13 +1204,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1280,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1330,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1396,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1446,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1512,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1562,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1551,22 +1575,22 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A67353D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1623,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1642,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1678,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1739,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1758,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1794,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1855,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1874,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1886,35 +1910,35 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1971,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1990,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2015,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2091,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2110,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2118,35 +2146,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2207,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2226,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2262,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2323,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2342,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,7 +2367,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2350,35 +2378,35 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2439,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2458,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,7 +2483,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2466,7 +2494,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2479,22 +2507,22 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2555,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2574,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,25 +2610,25 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2610,41 +2638,37 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2652,7 +2676,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2676,17 +2700,17 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2696,45 +2720,41 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2772,7 +2792,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2786,7 +2806,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2822,35 +2842,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2888,7 +2908,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2902,7 +2922,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2938,35 +2958,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2999,12 +3019,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3018,7 +3038,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3054,7 +3074,3603 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-operations.xlsx
+++ b/data/export/2026-10-30-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD53"/>
+  <dimension ref="A1:AD81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,14 +843,14 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>73.0</t>
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -891,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -924,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -948,17 +952,17 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -968,13 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1007,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1040,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1064,17 +1076,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1084,13 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1133,24 +1149,24 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1160,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1199,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1247,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1280,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1304,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1396,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1420,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1479,32 +1511,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -1512,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1536,33 +1572,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1667,7 +1707,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1678,7 +1718,7 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1711,32 +1751,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1744,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1768,33 +1812,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1908,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1910,7 +1958,7 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1976,7 +2024,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2030,7 +2078,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2144,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2146,7 +2194,7 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2260,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2262,7 +2310,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2376,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2372,13 +2420,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2391,22 +2443,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2496,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2458,7 +2510,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2488,41 +2540,45 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2555,12 +2611,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2574,7 +2630,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2599,46 +2655,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2671,12 +2731,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2690,7 +2750,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2715,46 +2775,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2787,12 +2851,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2806,7 +2870,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2842,35 +2906,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2903,12 +2967,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2922,7 +2986,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2947,46 +3011,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3019,12 +3087,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3038,7 +3106,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3063,46 +3131,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3135,12 +3207,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3154,7 +3226,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3179,46 +3251,50 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3251,12 +3327,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3270,7 +3346,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3295,7 +3371,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3306,35 +3382,35 @@
       <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3367,12 +3443,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3386,7 +3462,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3411,18 +3487,22 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3515,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3445,7 +3525,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3455,40 +3535,44 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3502,7 +3586,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3512,33 +3596,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3551,60 +3639,64 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3618,7 +3710,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3628,33 +3720,37 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3667,60 +3763,64 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3734,7 +3834,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3744,17 +3844,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3764,13 +3864,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3887,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3793,7 +3897,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3803,40 +3907,44 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3850,7 +3958,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3860,33 +3968,37 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3899,32 +4011,32 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq31，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3947,12 +4059,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3960,13 +4072,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4002,7 +4130,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4143,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4025,7 +4153,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4063,12 +4191,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4082,7 +4210,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4118,7 +4246,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4259,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4141,7 +4269,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4179,12 +4307,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4198,7 +4326,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4234,7 +4362,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4247,22 +4375,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4295,12 +4423,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4314,7 +4442,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4350,7 +4478,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4363,22 +4491,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4411,12 +4539,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4430,7 +4558,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4466,7 +4594,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4607,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4489,7 +4617,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4527,12 +4655,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4546,7 +4674,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4582,7 +4710,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4723,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4605,7 +4733,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4643,12 +4771,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4662,7 +4790,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4698,7 +4826,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4711,22 +4839,22 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4759,12 +4887,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4778,7 +4906,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4814,35 +4942,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4875,12 +5003,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4894,7 +5022,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4919,7 +5047,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4930,35 +5058,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4991,12 +5119,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5010,7 +5138,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5046,35 +5174,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5107,12 +5235,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5126,7 +5254,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5162,35 +5290,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5223,12 +5351,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5242,7 +5370,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5278,35 +5406,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5339,12 +5467,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5358,7 +5486,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5394,35 +5522,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5455,12 +5583,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5474,7 +5602,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5510,35 +5638,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5571,12 +5699,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5590,7 +5718,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5626,35 +5754,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5687,12 +5815,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5706,7 +5834,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5742,35 +5870,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5803,12 +5931,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5822,7 +5950,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5858,35 +5986,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5919,12 +6047,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5938,7 +6066,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5974,35 +6102,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6035,12 +6163,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6054,7 +6182,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6090,35 +6218,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6151,12 +6279,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6170,7 +6298,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6206,35 +6334,35 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6272,7 +6400,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6286,7 +6414,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6322,35 +6450,35 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A53062D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6383,12 +6511,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6402,7 +6530,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6438,35 +6566,35 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A57383A</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6504,7 +6632,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6518,7 +6646,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6554,35 +6682,35 @@
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6615,12 +6743,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6634,7 +6762,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6659,7 +6787,7 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
@@ -6670,7 +6798,3327 @@
       <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>110分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>101分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-operations.xlsx
+++ b/data/export/2026-10-30-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD81"/>
+  <dimension ref="A1:AD104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,22 +967,22 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1635,32 +1635,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -1668,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1692,17 +1696,17 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1712,13 +1716,17 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1761,24 +1769,24 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1788,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1837,7 +1845,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -1875,32 +1883,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1908,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1932,33 +1944,37 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1991,32 +2007,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2024,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2048,37 +2068,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2111,32 +2131,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2144,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2168,33 +2192,37 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2288,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2299,7 +2327,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2343,32 +2371,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2376,7 +2408,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2400,37 +2432,37 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2463,32 +2495,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2496,7 +2532,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2520,17 +2556,17 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2540,12 +2576,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
@@ -2583,32 +2619,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2616,7 +2656,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2640,32 +2680,32 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
@@ -2736,7 +2776,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2790,7 +2830,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2896,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2972,7 +3012,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3026,7 +3066,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3132,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3146,7 +3186,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3252,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3266,7 +3306,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3372,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3376,13 +3416,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3492,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3497,7 +3541,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
@@ -3509,70 +3553,66 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3586,7 +3626,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3596,17 +3636,17 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3621,82 +3661,78 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3710,7 +3746,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3720,107 +3756,103 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3834,7 +3866,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3844,107 +3876,103 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3958,7 +3986,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3968,17 +3996,17 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3988,55 +4016,51 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr">
-        <is>
-          <t>148.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq31，推进3站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4059,12 +4083,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4072,29 +4096,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>物理seq27（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>07:53</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>08:02</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4119,46 +4127,50 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4191,12 +4203,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4210,7 +4222,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4235,18 +4247,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4259,52 +4275,56 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4312,7 +4332,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4326,7 +4346,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4336,33 +4356,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4399,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4385,7 +4409,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4395,40 +4419,44 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4442,7 +4470,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4452,33 +4480,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4523,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4501,7 +4533,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4511,40 +4543,44 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4558,7 +4594,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4568,33 +4604,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4607,60 +4647,64 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4674,7 +4718,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4684,33 +4728,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4723,32 +4771,32 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4771,12 +4819,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4784,13 +4832,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4815,7 +4879,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4839,60 +4903,64 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4906,7 +4974,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4916,33 +4984,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4955,7 +5027,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4965,7 +5037,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4975,40 +5047,44 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5022,7 +5098,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5032,33 +5108,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5071,60 +5151,64 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5138,7 +5222,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5148,33 +5232,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5187,60 +5275,64 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5254,7 +5346,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5264,33 +5356,37 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5303,7 +5399,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5313,7 +5409,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5351,12 +5447,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5370,7 +5466,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5395,7 +5491,7 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5419,7 +5515,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5429,7 +5525,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5467,12 +5563,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5486,7 +5582,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5535,32 +5631,32 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq59，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5583,12 +5679,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5596,13 +5692,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5651,7 +5763,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5661,7 +5773,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5699,12 +5811,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5718,7 +5830,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5767,7 +5879,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5777,7 +5889,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5815,12 +5927,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5834,7 +5946,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5883,7 +5995,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5893,7 +6005,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5903,12 +6015,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq37推进至seq52，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -5931,12 +6043,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5944,13 +6056,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr"/>
-      <c r="T46" s="2" t="inlineStr"/>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq22映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5999,22 +6127,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6047,12 +6175,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6066,7 +6194,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6115,22 +6243,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6163,12 +6291,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6182,7 +6310,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6231,22 +6359,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6279,12 +6407,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6298,7 +6426,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6347,22 +6475,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6395,12 +6523,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6414,7 +6542,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6463,7 +6591,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6473,7 +6601,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6511,12 +6639,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6530,7 +6658,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6579,7 +6707,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A57383A</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6589,7 +6717,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6627,12 +6755,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6646,7 +6774,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6695,7 +6823,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6705,7 +6833,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6743,12 +6871,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6762,7 +6890,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6811,7 +6939,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -6821,7 +6949,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6859,12 +6987,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6878,7 +7006,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6903,22 +7031,18 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6931,7 +7055,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -6941,7 +7065,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6979,12 +7103,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6998,7 +7122,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7023,22 +7147,18 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>136.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7171,7 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -7061,7 +7181,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -7104,7 +7224,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7118,7 +7238,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7143,84 +7263,76 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>148.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7228,7 +7340,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7242,7 +7354,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7252,99 +7364,91 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A57383A</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>110分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7352,7 +7456,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7366,7 +7470,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7376,107 +7480,99 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7490,7 +7586,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7500,107 +7596,99 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7614,7 +7702,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7624,17 +7712,17 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7649,82 +7737,78 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7738,7 +7822,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7748,17 +7832,17 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7773,40 +7857,40 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7839,12 +7923,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7858,7 +7942,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7888,41 +7972,45 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7955,12 +8043,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7974,7 +8062,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7999,46 +8087,50 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8071,12 +8163,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8090,7 +8182,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8126,35 +8218,35 @@
       <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8187,12 +8279,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8206,7 +8298,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8231,46 +8323,50 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8303,12 +8399,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8322,7 +8418,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8347,46 +8443,50 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8419,12 +8519,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8438,7 +8538,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8463,46 +8563,50 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8535,12 +8639,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8554,7 +8658,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8579,46 +8683,50 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8651,12 +8759,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8670,7 +8778,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8695,7 +8803,7 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
@@ -8706,7 +8814,7 @@
       <c r="AC69" s="2" t="inlineStr"/>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8827,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A53062D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8729,50 +8837,54 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
           <t>07:42</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8786,7 +8898,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8796,33 +8908,37 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8835,52 +8951,56 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>07:47</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8888,7 +9008,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8902,7 +9022,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8912,33 +9032,37 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8951,7 +9075,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8961,7 +9085,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8971,40 +9095,44 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9018,7 +9146,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9028,33 +9156,37 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9067,7 +9199,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9077,7 +9209,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9087,40 +9219,44 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9134,7 +9270,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9144,22 +9280,22 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
@@ -9169,12 +9305,12 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9187,60 +9323,64 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35683D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9254,7 +9394,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9264,33 +9404,37 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB74" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9303,7 +9447,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9313,7 +9457,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9323,40 +9467,44 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9370,7 +9518,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9380,17 +9528,17 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9405,12 +9553,12 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9423,60 +9571,64 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9490,7 +9642,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9500,17 +9652,17 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9525,12 +9677,12 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9695,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9553,7 +9705,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9563,40 +9715,44 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9610,7 +9766,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9620,17 +9776,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9645,12 +9801,12 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9663,7 +9819,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -9673,7 +9829,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9683,40 +9839,44 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9730,7 +9890,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9740,17 +9900,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9765,12 +9925,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9943,7 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -9793,7 +9953,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -9803,40 +9963,44 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9850,7 +10014,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9860,33 +10024,37 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB79" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9899,22 +10067,22 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9947,12 +10115,12 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9966,7 +10134,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -10015,60 +10183,64 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10082,43 +10254,2799 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="W81" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X81" s="2" t="inlineStr">
+      <c r="X93" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y81" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z81" s="2" t="inlineStr">
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
+      <c r="AA93" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB81" s="2" t="inlineStr">
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC81" s="2" t="inlineStr"/>
-      <c r="AD81" s="2" t="inlineStr">
+      <c r="AC99" s="2" t="inlineStr"/>
+      <c r="AD99" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD100" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD101" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr"/>
+      <c r="AD102" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AD103" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr"/>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD104" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-operations.xlsx
+++ b/data/export/2026-10-30-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2088,17 +2088,17 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2212,17 +2212,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2456,12 +2456,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3568,17 +3568,17 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3816,17 +3816,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3940,17 +3940,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5180,17 +5180,17 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5304,17 +5304,17 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5428,17 +5428,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6416,17 +6416,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AD53" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7280,17 +7280,17 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7360,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7404,17 +7404,17 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8272,17 +8272,17 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8406,7 +8406,7 @@
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8520,17 +8520,17 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8768,17 +8768,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10252,17 +10252,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10624,17 +10624,17 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10948,7 +10948,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10992,12 +10992,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
@@ -11417,12 +11417,12 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11493,7 +11493,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11651,32 +11651,36 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11684,7 +11688,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11708,17 +11712,17 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
@@ -11728,17 +11732,17 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -11771,32 +11775,36 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11804,7 +11812,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11828,17 +11836,17 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
@@ -11848,17 +11856,17 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11891,32 +11899,36 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11924,7 +11936,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11948,17 +11960,17 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11968,17 +11980,17 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -12011,32 +12023,36 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:33</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -12044,7 +12060,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12068,17 +12084,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -12088,12 +12104,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
@@ -12131,32 +12147,36 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -12164,7 +12184,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12188,17 +12208,17 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
@@ -12208,12 +12228,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
@@ -12284,7 +12304,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12404,7 +12424,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12448,17 +12468,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -12528,7 +12548,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12572,17 +12592,17 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -12706,7 +12726,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -12954,7 +12974,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -13156,7 +13176,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13210,7 +13230,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13354,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -13458,7 +13478,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -13582,7 +13602,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -13652,7 +13672,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13706,7 +13726,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -13776,7 +13796,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13820,17 +13840,17 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -14036,7 +14056,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14080,17 +14100,17 @@
       </c>
       <c r="AB110" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -14280,7 +14300,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14474,7 +14494,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -14598,7 +14618,7 @@
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -14718,7 +14738,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -14788,7 +14808,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14842,7 +14862,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -14908,7 +14928,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -15028,7 +15048,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15082,7 +15102,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -15206,7 +15226,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -15330,7 +15350,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -15400,7 +15420,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15454,7 +15474,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -15578,7 +15598,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -15702,7 +15722,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -15768,7 +15788,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15817,7 +15837,7 @@
       </c>
       <c r="AC124" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD124" s="2" t="inlineStr">
@@ -16058,7 +16078,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -16124,7 +16144,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16168,17 +16188,17 @@
       </c>
       <c r="AB127" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC127" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -16298,7 +16318,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -16620,7 +16640,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16674,7 +16694,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -16798,7 +16818,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -16922,7 +16942,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -17042,7 +17062,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -17112,7 +17132,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17166,7 +17186,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -17236,7 +17256,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17280,17 +17300,17 @@
       </c>
       <c r="AB136" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC136" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -17484,7 +17504,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17528,17 +17548,17 @@
       </c>
       <c r="AB138" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC138" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -17658,7 +17678,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -17782,7 +17802,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -17906,7 +17926,7 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -17972,7 +17992,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18092,7 +18112,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18146,7 +18166,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -18216,7 +18236,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18270,7 +18290,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -18394,7 +18414,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -18464,7 +18484,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18518,7 +18538,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -18642,7 +18662,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -18890,7 +18910,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -19014,7 +19034,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -19080,7 +19100,7 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -19460,7 +19480,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19638,7 +19658,7 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -19762,7 +19782,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -19886,7 +19906,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -19956,7 +19976,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20010,7 +20030,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -20134,7 +20154,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -20258,7 +20278,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20402,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -20506,7 +20526,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -20630,7 +20650,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20774,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -21076,7 +21096,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -21120,17 +21140,17 @@
       </c>
       <c r="AB167" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC167" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -21196,7 +21216,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21312,7 +21332,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21361,7 +21381,7 @@
       </c>
       <c r="AC169" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD169" s="2" t="inlineStr">
@@ -21436,7 +21456,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21560,7 +21580,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21604,17 +21624,17 @@
       </c>
       <c r="AB171" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -21684,7 +21704,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21738,7 +21758,7 @@
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -21808,7 +21828,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21852,17 +21872,17 @@
       </c>
       <c r="AB173" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC173" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -21932,7 +21952,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -21986,7 +22006,7 @@
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -22056,7 +22076,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22110,7 +22130,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -22304,7 +22324,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22358,7 +22378,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -22482,7 +22502,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -22602,7 +22622,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -22722,7 +22742,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -22970,7 +22990,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -23094,7 +23114,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -23218,7 +23238,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -23342,7 +23362,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -23528,7 +23548,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23698,7 +23718,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -23731,32 +23751,36 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr"/>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N189" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
           <t>17:41</t>
@@ -23764,7 +23788,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23788,17 +23812,17 @@
       </c>
       <c r="X189" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z189" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA189" s="2" t="inlineStr">
@@ -23808,13 +23832,17 @@
       </c>
       <c r="AB189" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC189" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC189" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -23857,12 +23885,12 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
@@ -23884,7 +23912,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23933,7 +23961,7 @@
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
@@ -23971,32 +23999,36 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N191" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -24004,7 +24036,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24028,17 +24060,17 @@
       </c>
       <c r="X191" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z191" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA191" s="2" t="inlineStr">
@@ -24048,17 +24080,17 @@
       </c>
       <c r="AB191" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC191" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -24091,12 +24123,12 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq29推进至seq62，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
@@ -24124,7 +24156,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24132,10 +24164,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R192" s="2" t="inlineStr"/>
-      <c r="S192" s="2" t="inlineStr"/>
-      <c r="T192" s="2" t="inlineStr"/>
-      <c r="U192" s="2" t="inlineStr"/>
+      <c r="R192" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S192" s="2" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="U192" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置锦绣路花木路 ETA 5分钟参与校验</t>
+        </is>
+      </c>
       <c r="V192" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -24178,7 +24226,7 @@
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -24211,32 +24259,36 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr"/>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N193" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24244,7 +24296,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24268,17 +24320,17 @@
       </c>
       <c r="X193" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z193" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA193" s="2" t="inlineStr">
@@ -24288,17 +24340,17 @@
       </c>
       <c r="AB193" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC193" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -24331,32 +24383,36 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr"/>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N194" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -24364,7 +24420,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24388,17 +24444,17 @@
       </c>
       <c r="X194" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z194" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA194" s="2" t="inlineStr">
@@ -24408,17 +24464,17 @@
       </c>
       <c r="AB194" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC194" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -24484,7 +24540,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24604,7 +24660,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24658,7 +24714,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -24724,7 +24780,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24778,7 +24834,7 @@
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -24844,7 +24900,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24898,7 +24954,7 @@
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -24964,7 +25020,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25018,7 +25074,7 @@
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -25138,7 +25194,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -25204,7 +25260,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25324,7 +25380,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25368,17 +25424,17 @@
       </c>
       <c r="AB202" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC202" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -25502,7 +25558,7 @@
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -25820,7 +25876,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25874,7 +25930,7 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -25944,7 +26000,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -25998,7 +26054,7 @@
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -26122,7 +26178,7 @@
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -26246,7 +26302,7 @@
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -26316,7 +26372,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26360,17 +26416,17 @@
       </c>
       <c r="AB210" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC210" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -26440,7 +26496,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
@@ -26484,17 +26540,17 @@
       </c>
       <c r="AB211" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC211" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -26614,7 +26670,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -26862,7 +26918,7 @@
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -26986,7 +27042,7 @@
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -27230,7 +27286,7 @@
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -27300,7 +27356,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -27344,17 +27400,17 @@
       </c>
       <c r="AB218" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC218" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -27420,7 +27476,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27464,17 +27520,17 @@
       </c>
       <c r="AB219" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC219" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -27718,7 +27774,7 @@
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -27912,7 +27968,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q223" s="2" t="inlineStr">
@@ -27966,7 +28022,7 @@
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -28148,7 +28204,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -28202,7 +28258,7 @@
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -28326,7 +28382,7 @@
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -28450,7 +28506,7 @@
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -28516,7 +28572,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28560,17 +28616,17 @@
       </c>
       <c r="AB228" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -28640,7 +28696,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28684,17 +28740,17 @@
       </c>
       <c r="AB229" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -28942,7 +28998,7 @@
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -29066,7 +29122,7 @@
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -29260,7 +29316,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q234" s="2" t="inlineStr">
@@ -29304,17 +29360,17 @@
       </c>
       <c r="AB234" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC234" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -29438,7 +29494,7 @@
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -29752,7 +29808,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q238" s="2" t="inlineStr">
@@ -29806,7 +29862,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -29930,7 +29986,7 @@
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -30054,7 +30110,7 @@
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -30120,7 +30176,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -30176,17 +30232,17 @@
       </c>
       <c r="AB241" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC241" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -30434,7 +30490,7 @@
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -30682,7 +30738,7 @@
       </c>
       <c r="AD245" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -30806,7 +30862,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -31178,7 +31234,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -31302,7 +31358,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -31550,7 +31606,7 @@
       </c>
       <c r="AD252" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -31798,7 +31854,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -31922,7 +31978,7 @@
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -32240,7 +32296,7 @@
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q258" s="2" t="inlineStr">
@@ -32284,17 +32340,17 @@
       </c>
       <c r="AB258" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC258" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -32418,7 +32474,7 @@
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -32538,7 +32594,7 @@
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -32786,7 +32842,7 @@
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -32856,7 +32912,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -32910,7 +32966,7 @@
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -33034,7 +33090,7 @@
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -33228,7 +33284,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33272,17 +33328,17 @@
       </c>
       <c r="AB266" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC266" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -33402,7 +33458,7 @@
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -33526,7 +33582,7 @@
       </c>
       <c r="AD268" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -33596,7 +33652,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33650,7 +33706,7 @@
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -33720,7 +33776,7 @@
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q270" s="2" t="inlineStr">
@@ -33764,17 +33820,17 @@
       </c>
       <c r="AB270" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC270" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -33898,7 +33954,7 @@
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -34092,7 +34148,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q273" s="2" t="inlineStr">
@@ -34136,17 +34192,17 @@
       </c>
       <c r="AB273" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC273" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -34394,7 +34450,7 @@
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -34460,7 +34516,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34504,17 +34560,17 @@
       </c>
       <c r="AB276" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -34762,7 +34818,7 @@
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -34886,7 +34942,7 @@
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -35010,7 +35066,7 @@
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -35076,7 +35132,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35130,7 +35186,7 @@
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -35316,7 +35372,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35360,17 +35416,17 @@
       </c>
       <c r="AB283" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -35494,7 +35550,7 @@
       </c>
       <c r="AD284" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -35618,7 +35674,7 @@
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -35688,7 +35744,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35742,7 +35798,7 @@
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -35812,7 +35868,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35856,17 +35912,17 @@
       </c>
       <c r="AB287" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -35990,7 +36046,7 @@
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -36234,7 +36290,7 @@
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -36304,7 +36360,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q291" s="2" t="inlineStr">
@@ -36348,17 +36404,17 @@
       </c>
       <c r="AB291" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC291" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD291" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -36676,7 +36732,7 @@
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q294" s="2" t="inlineStr">
@@ -36720,17 +36776,17 @@
       </c>
       <c r="AB294" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC294" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD294" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -36854,7 +36910,7 @@
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -36978,7 +37034,7 @@
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -37102,7 +37158,7 @@
       </c>
       <c r="AD297" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -37172,7 +37228,7 @@
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q298" s="2" t="inlineStr">
@@ -37226,7 +37282,7 @@
       </c>
       <c r="AD298" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -37296,7 +37352,7 @@
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q299" s="2" t="inlineStr">
@@ -37350,7 +37406,7 @@
       </c>
       <c r="AD299" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -37383,32 +37439,36 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K300" s="2" t="inlineStr"/>
       <c r="L300" s="2" t="inlineStr"/>
       <c r="M300" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N300" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N300" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O300" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -37416,7 +37476,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37440,17 +37500,17 @@
       </c>
       <c r="X300" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y300" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z300" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA300" s="2" t="inlineStr">
@@ -37460,17 +37520,17 @@
       </c>
       <c r="AB300" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC300" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD300" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -37503,32 +37563,36 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K301" s="2" t="inlineStr"/>
       <c r="L301" s="2" t="inlineStr"/>
       <c r="M301" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N301" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N301" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O301" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -37536,7 +37600,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37560,17 +37624,17 @@
       </c>
       <c r="X301" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z301" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA301" s="2" t="inlineStr">
@@ -37580,17 +37644,17 @@
       </c>
       <c r="AB301" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC301" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -37623,32 +37687,36 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr"/>
       <c r="L302" s="2" t="inlineStr"/>
       <c r="M302" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N302" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N302" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O302" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -37656,7 +37724,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37680,17 +37748,17 @@
       </c>
       <c r="X302" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z302" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA302" s="2" t="inlineStr">
@@ -37700,17 +37768,17 @@
       </c>
       <c r="AB302" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -37743,32 +37811,36 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr"/>
       <c r="M303" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N303" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N303" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O303" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -37776,7 +37848,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37800,17 +37872,17 @@
       </c>
       <c r="X303" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z303" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA303" s="2" t="inlineStr">
@@ -37820,17 +37892,17 @@
       </c>
       <c r="AB303" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC303" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD303" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -37896,7 +37968,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -37950,7 +38022,7 @@
       </c>
       <c r="AD304" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -38016,7 +38088,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38060,17 +38132,17 @@
       </c>
       <c r="AB305" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -38136,7 +38208,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38180,17 +38252,17 @@
       </c>
       <c r="AB306" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC306" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD306" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-operations.xlsx
+++ b/data/export/2026-10-30-operations.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1716,12 +1716,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -12157,24 +12157,24 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>21:46</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
@@ -12271,32 +12271,36 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -12304,7 +12308,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12328,17 +12332,17 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA96" s="2" t="inlineStr">
@@ -12348,12 +12352,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
@@ -12424,7 +12428,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12726,7 +12730,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -12974,7 +12978,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -13176,7 +13180,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13220,17 +13224,17 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -13354,7 +13358,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -13478,7 +13482,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13606,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -13672,7 +13676,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13716,17 +13720,17 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -13850,7 +13854,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -14494,7 +14498,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -14618,7 +14622,7 @@
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -14808,7 +14812,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14852,17 +14856,17 @@
       </c>
       <c r="AB116" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -15048,7 +15052,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15092,17 +15096,17 @@
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -15226,7 +15230,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -15350,7 +15354,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -15474,7 +15478,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -15598,7 +15602,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -15722,7 +15726,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -16078,7 +16082,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -16318,7 +16322,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -16640,7 +16644,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16684,17 +16688,17 @@
       </c>
       <c r="AB131" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC131" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -16818,7 +16822,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -16942,7 +16946,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -17062,7 +17066,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -17132,7 +17136,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17176,17 +17180,17 @@
       </c>
       <c r="AB135" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -17310,7 +17314,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -17678,7 +17682,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -17802,7 +17806,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -18112,7 +18116,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18156,17 +18160,17 @@
       </c>
       <c r="AB143" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC143" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -18236,7 +18240,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18280,17 +18284,17 @@
       </c>
       <c r="AB144" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC144" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18418,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -18538,7 +18542,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -18662,7 +18666,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -18910,7 +18914,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19038,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -19782,7 +19786,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -19906,7 +19910,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -19976,7 +19980,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20020,17 +20024,17 @@
       </c>
       <c r="AB158" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC158" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20158,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -20278,7 +20282,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -20402,7 +20406,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -20526,7 +20530,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -20650,7 +20654,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -20774,7 +20778,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -21150,7 +21154,7 @@
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -21704,7 +21708,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21748,17 +21752,17 @@
       </c>
       <c r="AB172" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -22006,7 +22010,7 @@
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -22076,7 +22080,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22120,17 +22124,17 @@
       </c>
       <c r="AB175" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC175" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -22324,7 +22328,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22368,17 +22372,17 @@
       </c>
       <c r="AB177" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -22502,7 +22506,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -22622,7 +22626,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -22742,7 +22746,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -23114,7 +23118,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -23238,7 +23242,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -23362,7 +23366,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -23718,7 +23722,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -23842,7 +23846,7 @@
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -24090,7 +24094,7 @@
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -24226,7 +24230,7 @@
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -24627,32 +24631,36 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr"/>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N196" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -24660,7 +24668,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24684,17 +24692,17 @@
       </c>
       <c r="X196" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z196" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA196" s="2" t="inlineStr">
@@ -24704,17 +24712,17 @@
       </c>
       <c r="AB196" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC196" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -24747,32 +24755,36 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr"/>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N197" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N197" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -24780,7 +24792,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24804,17 +24816,17 @@
       </c>
       <c r="X197" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z197" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA197" s="2" t="inlineStr">
@@ -24824,17 +24836,17 @@
       </c>
       <c r="AB197" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -24867,32 +24879,36 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr"/>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N198" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -24900,7 +24916,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24924,17 +24940,17 @@
       </c>
       <c r="X198" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z198" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA198" s="2" t="inlineStr">
@@ -24944,17 +24960,17 @@
       </c>
       <c r="AB198" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC198" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -24987,32 +25003,36 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:12</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr"/>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N199" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -25020,7 +25040,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25044,17 +25064,17 @@
       </c>
       <c r="X199" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z199" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA199" s="2" t="inlineStr">
@@ -25064,17 +25084,17 @@
       </c>
       <c r="AB199" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -25194,7 +25214,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -25380,7 +25400,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25429,12 +25449,12 @@
       </c>
       <c r="AC202" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -25682,7 +25702,7 @@
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -25806,7 +25826,7 @@
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -25930,7 +25950,7 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -26000,7 +26020,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -26044,17 +26064,17 @@
       </c>
       <c r="AB207" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -26178,7 +26198,7 @@
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -26302,7 +26322,7 @@
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -26372,7 +26392,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26416,17 +26436,17 @@
       </c>
       <c r="AB210" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC210" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -26550,7 +26570,7 @@
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -27042,7 +27062,7 @@
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -27286,7 +27306,7 @@
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -27356,7 +27376,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -27405,12 +27425,12 @@
       </c>
       <c r="AC218" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -27476,7 +27496,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27530,7 +27550,7 @@
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -27654,7 +27674,7 @@
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -27898,7 +27918,7 @@
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -28022,7 +28042,7 @@
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -28204,7 +28224,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -28248,17 +28268,17 @@
       </c>
       <c r="AB225" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC225" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -28382,7 +28402,7 @@
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -28506,7 +28526,7 @@
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -28626,7 +28646,7 @@
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -28696,7 +28716,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28740,17 +28760,17 @@
       </c>
       <c r="AB229" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -29316,7 +29336,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q234" s="2" t="inlineStr">
@@ -29370,7 +29390,7 @@
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -29618,7 +29638,7 @@
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -29742,7 +29762,7 @@
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -29862,7 +29882,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -29986,7 +30006,7 @@
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -30110,7 +30130,7 @@
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -30242,7 +30262,7 @@
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -30986,7 +31006,7 @@
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -31110,7 +31130,7 @@
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -31234,7 +31254,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -31358,7 +31378,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -32102,7 +32122,7 @@
       </c>
       <c r="AD256" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -32226,7 +32246,7 @@
       </c>
       <c r="AD257" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -32296,7 +32316,7 @@
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q258" s="2" t="inlineStr">
@@ -32345,12 +32365,12 @@
       </c>
       <c r="AC258" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -32474,7 +32494,7 @@
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -32594,7 +32614,7 @@
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -32912,7 +32932,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -32956,17 +32976,17 @@
       </c>
       <c r="AB263" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -33090,7 +33110,7 @@
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -33284,7 +33304,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33328,17 +33348,17 @@
       </c>
       <c r="AB266" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC266" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -33458,7 +33478,7 @@
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -33706,7 +33726,7 @@
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -33776,7 +33796,7 @@
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q270" s="2" t="inlineStr">
@@ -33830,7 +33850,7 @@
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -34078,7 +34098,7 @@
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -34202,7 +34222,7 @@
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -34326,7 +34346,7 @@
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -34450,7 +34470,7 @@
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -34516,7 +34536,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34565,12 +34585,12 @@
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -34818,7 +34838,7 @@
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -35066,7 +35086,7 @@
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -35132,7 +35152,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35176,17 +35196,17 @@
       </c>
       <c r="AB281" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC281" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -35372,7 +35392,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35416,17 +35436,17 @@
       </c>
       <c r="AB283" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -35550,7 +35570,7 @@
       </c>
       <c r="AD284" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -35798,7 +35818,7 @@
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35888,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35922,7 +35942,7 @@
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -36166,7 +36186,7 @@
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -36290,7 +36310,7 @@
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -36414,7 +36434,7 @@
       </c>
       <c r="AD291" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -36538,7 +36558,7 @@
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -36732,7 +36752,7 @@
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q294" s="2" t="inlineStr">
@@ -36781,12 +36801,12 @@
       </c>
       <c r="AC294" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD294" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -36910,7 +36930,7 @@
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -37158,7 +37178,7 @@
       </c>
       <c r="AD297" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -37228,7 +37248,7 @@
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q298" s="2" t="inlineStr">
@@ -37272,17 +37292,17 @@
       </c>
       <c r="AB298" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC298" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD298" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -37406,7 +37426,7 @@
       </c>
       <c r="AD299" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -37476,7 +37496,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37520,17 +37540,17 @@
       </c>
       <c r="AB300" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC300" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD300" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -37654,7 +37674,7 @@
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -37724,7 +37744,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37778,7 +37798,7 @@
       </c>
       <c r="AD302" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -37821,24 +37841,24 @@
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr"/>
       <c r="M303" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N303" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O303" s="2" t="inlineStr">
@@ -37848,7 +37868,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37897,12 +37917,12 @@
       </c>
       <c r="AC303" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD303" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -37935,32 +37955,36 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="2" t="inlineStr"/>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N304" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N304" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O304" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -37968,7 +37992,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -37992,17 +38016,17 @@
       </c>
       <c r="X304" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z304" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA304" s="2" t="inlineStr">
@@ -38012,17 +38036,17 @@
       </c>
       <c r="AB304" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -38055,32 +38079,36 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:24</t>
         </is>
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr"/>
       <c r="L305" s="2" t="inlineStr"/>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N305" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N305" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O305" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -38088,7 +38116,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38112,17 +38140,17 @@
       </c>
       <c r="X305" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z305" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA305" s="2" t="inlineStr">
@@ -38132,17 +38160,17 @@
       </c>
       <c r="AB305" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -38208,7 +38236,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38262,7 +38290,7 @@
       </c>
       <c r="AD306" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
